--- a/12-06-26/zeshan.xlsx
+++ b/12-06-26/zeshan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8666F2BE-A6A7-4039-BC51-C755F73EB3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FEF28B-2B17-4FDA-93B4-6FBF37F317D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3414,7 +3414,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3442,7 +3442,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4637,7 +4637,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4665,7 +4665,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5860,7 +5860,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5888,7 +5888,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7083,7 +7083,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7111,7 +7111,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8306,7 +8306,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8334,7 +8334,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9529,7 +9529,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9557,7 +9557,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10747,7 +10747,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10775,7 +10775,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11982,7 +11982,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -12010,7 +12010,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13212,7 +13212,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13240,7 +13240,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14454,7 +14454,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14482,7 +14482,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18421,7 +18421,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18449,7 +18449,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19638,7 +19638,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19666,7 +19666,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20855,7 +20855,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20883,7 +20883,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -22072,7 +22072,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22100,7 +22100,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23294,7 +23294,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23322,7 +23322,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24761,7 +24761,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24789,7 +24789,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25990,7 +25990,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -26018,7 +26018,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27219,7 +27219,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27247,7 +27247,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28443,7 +28443,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28471,7 +28471,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29666,7 +29666,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29694,7 +29694,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30889,7 +30889,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30917,7 +30917,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
